--- a/models/sovereigns/Armenia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Armenia_Sovereign_Model.xlsx
@@ -764,16 +764,34 @@
           <t>gov_debt_pct_gdp</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n"/>
+      <c r="B8" s="2" t="n">
+        <v>50.6</v>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -915,16 +933,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>2.421</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1070,16 +1106,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>31.873</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Armenia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Armenia_Sovereign_Model.xlsx
@@ -647,12 +647,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CBA</t>
+          <t>Central Bank of Armenia, refinancing rate decision</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -700,12 +700,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Armstat</t>
+          <t>Armstat, Consumer Price Index</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF</t>
+          <t>IMF (one of IMF 5.25%, World Bank 5.3%, EBRD 5.5%, Fitch 5.2% forecasts)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>15-Jun-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -826,17 +826,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2026 (tracking, state budget deficit)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance</t>
+          <t>Ministry of Finance, State Budget Execution</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oct-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -913,19 +913,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Armstat</t>
+          <t>Armstat, Balance of Payments Q2 2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jun-26</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>quarterly, USD 749.7m deficit</t>
-        </is>
-      </c>
+          <t>30-Jun-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -983,17 +979,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CBA</t>
+          <t>Central Bank of Armenia, Gross International Reserves Report</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross international reserves</t>
+          <t>CBA gross international reserves, reported as exceeding USD 6.5bn; gold treatment not stated</t>
         </is>
       </c>
     </row>
@@ -1035,19 +1031,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CBA</t>
+          <t>Central Bank of Armenia (reported as more than 5 months; value is a lower bound)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sep-26</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>stated as over 5 months</t>
-        </is>
-      </c>
+          <t>30-Sep-26</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1299,8 +1291,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Precautionary SBA (3-year)</t>
-        </is>
+          <t>Stand-By Arrangement (3-year, precautionary)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0502</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1360,7 +1355,11 @@
       <c r="B3" s="2" t="n">
         <v>5.25</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IMF forecast, 15-Jun-26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1389,7 +1388,11 @@
       <c r="B6" s="2" t="n">
         <v>-3.4</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ministry of Finance, Oct-26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/models/sovereigns/Armenia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Armenia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/armenia.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/armenia.json</t>
         </is>
       </c>
     </row>
@@ -700,12 +700,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Armstat, Consumer Price Index</t>
+          <t>Armstat Consumer Price Index</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -726,17 +726,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2026F</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF (one of IMF 5.25%, World Bank 5.3%, EBRD 5.5%, Fitch 5.2% forecasts)</t>
+          <t>IMF forecast (World Bank 5.3, EBRD 5.5, Fitch 5.2)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -826,7 +826,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026 (tracking, state budget deficit)</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>Oct-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Armstat, Balance of Payments Q2 2026</t>
+          <t>Armstat Balance of Payments Q2 2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30-Jun-26</t>
+          <t>Jun-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -984,12 +984,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBA gross international reserves, reported as exceeding USD 6.5bn; gold treatment not stated</t>
+          <t>CBA gross international reserves, reported as exceeding USD 6.5bn</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Central Bank of Armenia (reported as more than 5 months; value is a lower bound)</t>
+          <t>Central Bank of Armenia (reported as more than 5 months)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Stand-By Arrangement (3-year, precautionary)</t>
+          <t>3-year precautionary Stand-By Arrangement</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1328,10 +1328,20 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2026F</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -1344,7 +1354,9 @@
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1352,12 +1364,16 @@
           <t>real_gdp_growth_pct</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n">
         <v>5.25</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>IMF forecast, 15-Jun-26</t>
+      <c r="D3" s="2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>IMF, Jun-26</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1384,9 @@
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1377,7 +1395,9 @@
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1385,10 +1405,12 @@
           <t>fiscal_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n">
         <v>-3.4</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Ministry of Finance, Oct-26</t>
         </is>
@@ -1401,7 +1423,9 @@
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1410,7 +1434,9 @@
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1419,7 +1445,9 @@
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1427,8 +1455,18 @@
           <t>gross_reserves_usd_bn</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Central Bank of Armenia, 2023 value is late 2023 (approximate, 'USD 3.6bn in late 2023') and 2026 value is Sep-26</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1437,7 +1475,9 @@
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1446,7 +1486,9 @@
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Armenia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Armenia_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Central Bank of Armenia, refinancing rate decision</t>
+          <t>Central Bank of Armenia (refinancing rate)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Armstat Consumer Price Index</t>
+          <t>Armstat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF forecast (World Bank 5.3, EBRD 5.5, Fitch 5.2)</t>
+          <t>IMF (full-year 2026 projection)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance, State Budget Execution</t>
+          <t>Ministry of Finance, State Budget Execution (tracking vs 4.5% target)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Armstat Balance of Payments Q2 2026</t>
+          <t>Armstat, Balance of Payments Q2 2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Central Bank of Armenia, Gross International Reserves Report</t>
+          <t>Central Bank of Armenia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBA gross international reserves, reported as exceeding USD 6.5bn</t>
+          <t>CBA gross international reserves; reported as exceeding USD 6.5bn; gold inclusion not specified</t>
         </is>
       </c>
     </row>
@@ -1291,11 +1291,8 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3-year precautionary Stand-By Arrangement</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0.0502</v>
+          <t>Stand-By Arrangement (3-year, precautionary)</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/models/sovereigns/Armenia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Armenia_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Central Bank of Armenia (refinancing rate)</t>
+          <t>Central Bank of Armenia refinancing rate decision</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026F</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF (full-year 2026 projection)</t>
+          <t>IMF projection cited in adjudicated document</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance, State Budget Execution (tracking vs 4.5% target)</t>
+          <t>Ministry of Finance state budget execution (tracking vs 4.5% target)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Armstat, Balance of Payments Q2 2026</t>
+          <t>Armstat balance of payments</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBA gross international reserves; reported as exceeding USD 6.5bn; gold inclusion not specified</t>
+          <t>CBA gross international reserves, stated as exceeding USD 6.5bn; gold treatment not stated</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Central Bank of Armenia (reported as more than 5 months)</t>
+          <t>Central Bank of Armenia (stated as more than 5 months)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1293,6 +1293,9 @@
         <is>
           <t>Stand-By Arrangement (3-year, precautionary)</t>
         </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0502</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1461,7 +1464,7 @@
       <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Central Bank of Armenia, 2023 value is late 2023 (approximate, 'USD 3.6bn in late 2023') and 2026 value is Sep-26</t>
+          <t>Central Bank of Armenia, late 2023 level cited in adjudicated document (approximate; 'late 2023' reference date)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Armenia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Armenia_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Central Bank of Armenia refinancing rate decision</t>
+          <t>Central Bank of Armenia, refinancing rate decision</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2026F</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF projection cited in adjudicated document</t>
+          <t>IMF (World Bank 5.3%, EBRD 5.5%, Fitch 5.2%)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance state budget execution (tracking vs 4.5% target)</t>
+          <t>Ministry of Finance, State Budget Execution</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Armstat balance of payments</t>
+          <t>Armstat, Balance of Payments Q2 2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBA gross international reserves, stated as exceeding USD 6.5bn; gold treatment not stated</t>
+          <t>CBA gross international reserves; document states 'exceeding USD 6.5bn', so a floor</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Central Bank of Armenia (stated as more than 5 months)</t>
+          <t>Central Bank of Armenia (stated as 'more than 5 months')</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Stand-By Arrangement (3-year, precautionary)</t>
+          <t>3-year precautionary Stand-By Arrangement</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1464,7 +1464,7 @@
       <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Central Bank of Armenia, late 2023 level cited in adjudicated document (approximate; 'late 2023' reference date)</t>
+          <t>Central Bank of Armenia, late 2023 (as cited in adjudicated document, Oct-26)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Armenia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Armenia_Sovereign_Model.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>15-Sep-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Armstat</t>
+          <t>Armstat Consumer Price Index</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026F</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF (World Bank 5.3%, EBRD 5.5%, Fitch 5.2%)</t>
+          <t>IMF (forecast cited in adjudicated document)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance, State Budget Execution</t>
+          <t>Ministry of Finance, State Budget Execution (deficit tracking)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Armstat, Balance of Payments Q2 2026</t>
+          <t>Armstat Balance of Payments Q2 2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Central Bank of Armenia</t>
+          <t>Central Bank of Armenia, Gross International Reserves Report</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBA gross international reserves; document states 'exceeding USD 6.5bn', so a floor</t>
+          <t>CBA gross international reserves (reported as exceeding USD 6.5bn; gold inclusion not stated)</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Central Bank of Armenia (stated as 'more than 5 months')</t>
+          <t>Central Bank of Armenia (reported as over 5 months)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1293,9 +1293,6 @@
         <is>
           <t>3-year precautionary Stand-By Arrangement</t>
         </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0.0502</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1373,7 +1370,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IMF, Jun-26</t>
+          <t>IMF forecast, Jun-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Armenia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Armenia_Sovereign_Model.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -700,12 +700,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Armstat Consumer Price Index</t>
+          <t>Armstat, Consumer Price Index</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IMF (forecast cited in adjudicated document)</t>
+          <t>IMF</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>30-Jun-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -826,17 +826,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2026 (tracking)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Finance, State Budget Execution (deficit tracking)</t>
+          <t>Ministry of Finance, State Budget Execution</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Armstat Balance of Payments Q2 2026</t>
+          <t>Armstat, Balance of Payments Q2 2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jun-26</t>
+          <t>30-Jun-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -979,17 +979,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Central Bank of Armenia, Gross International Reserves Report</t>
+          <t>Central Bank of Armenia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBA gross international reserves (reported as exceeding USD 6.5bn; gold inclusion not stated)</t>
+          <t>CBA gross international reserves; reported as exceeding USD 6.5bn; gold treatment not stated</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Central Bank of Armenia (reported as over 5 months)</t>
+          <t>Central Bank of Armenia (reported as more than 5 months)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IMF forecast, Jun-26</t>
+          <t>IMF, 30-Jun-26</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       <c r="D6" s="2" t="n"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ministry of Finance, Oct-26</t>
+          <t>Ministry of Finance, 09-Oct-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Armenia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Armenia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/armenia.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/armenia.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Armenia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Armenia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/armenia.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/armenia.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Armenia_Sovereign_Model.xlsx
+++ b/models/sovereigns/Armenia_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/armenia.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/armenia.json</t>
         </is>
       </c>
     </row>
